--- a/artfynd/A 46895-2024 artfynd.xlsx
+++ b/artfynd/A 46895-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1048,6 +1048,486 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126160247</v>
+      </c>
+      <c r="B5" t="n">
+        <v>43209</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100679</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Brun gräsfjäril</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Coenonympha hero</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1760)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Djupdalen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>415118</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6591451</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Alster</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Linnéa Skarped</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Linnéa Skarped</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126160239</v>
+      </c>
+      <c r="B6" t="n">
+        <v>43209</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100679</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Brun gräsfjäril</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Coenonympha hero</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1760)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Djupdalen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>415125</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6591405</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Alster</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Linnéa Skarped</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Linnéa Skarped</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126160263</v>
+      </c>
+      <c r="B7" t="n">
+        <v>43209</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100679</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Brun gräsfjäril</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Coenonympha hero</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1760)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Djupdalen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>414964</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6591421</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Alster</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Linnéa Skarped</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Linnéa Skarped</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126160258</v>
+      </c>
+      <c r="B8" t="n">
+        <v>43209</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100679</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Brun gräsfjäril</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Coenonympha hero</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1760)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Djupdalen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>414944</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6591392</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Alster</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Linnéa Skarped</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Linnéa Skarped</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46895-2024 artfynd.xlsx
+++ b/artfynd/A 46895-2024 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>126160247</v>
       </c>
       <c r="B5" t="n">
-        <v>43209</v>
+        <v>43210</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>126160239</v>
       </c>
       <c r="B6" t="n">
-        <v>43209</v>
+        <v>43210</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>126160263</v>
       </c>
       <c r="B7" t="n">
-        <v>43209</v>
+        <v>43210</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>126160258</v>
       </c>
       <c r="B8" t="n">
-        <v>43209</v>
+        <v>43210</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 46895-2024 artfynd.xlsx
+++ b/artfynd/A 46895-2024 artfynd.xlsx
@@ -1171,7 +1171,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126160239</v>
+        <v>126160263</v>
       </c>
       <c r="B6" t="n">
         <v>43210</v>
@@ -1219,13 +1219,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>415125</v>
+        <v>414964</v>
       </c>
       <c r="R6" t="n">
-        <v>6591405</v>
+        <v>6591421</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126160263</v>
+        <v>126160239</v>
       </c>
       <c r="B7" t="n">
         <v>43210</v>
@@ -1340,13 +1340,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>414964</v>
+        <v>415125</v>
       </c>
       <c r="R7" t="n">
-        <v>6591421</v>
+        <v>6591405</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>

--- a/artfynd/A 46895-2024 artfynd.xlsx
+++ b/artfynd/A 46895-2024 artfynd.xlsx
@@ -1171,7 +1171,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126160263</v>
+        <v>126160239</v>
       </c>
       <c r="B6" t="n">
         <v>43210</v>
@@ -1219,13 +1219,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>414964</v>
+        <v>415125</v>
       </c>
       <c r="R6" t="n">
-        <v>6591421</v>
+        <v>6591405</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126160239</v>
+        <v>126160263</v>
       </c>
       <c r="B7" t="n">
         <v>43210</v>
@@ -1340,13 +1340,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>415125</v>
+        <v>414964</v>
       </c>
       <c r="R7" t="n">
-        <v>6591405</v>
+        <v>6591421</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>

--- a/artfynd/A 46895-2024 artfynd.xlsx
+++ b/artfynd/A 46895-2024 artfynd.xlsx
@@ -1053,7 +1053,7 @@
         <v>126160247</v>
       </c>
       <c r="B5" t="n">
-        <v>43210</v>
+        <v>43211</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1174,7 +1174,7 @@
         <v>126160239</v>
       </c>
       <c r="B6" t="n">
-        <v>43210</v>
+        <v>43211</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>126160263</v>
       </c>
       <c r="B7" t="n">
-        <v>43210</v>
+        <v>43211</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
         <v>126160258</v>
       </c>
       <c r="B8" t="n">
-        <v>43210</v>
+        <v>43211</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 46895-2024 artfynd.xlsx
+++ b/artfynd/A 46895-2024 artfynd.xlsx
@@ -1171,7 +1171,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126160239</v>
+        <v>126160263</v>
       </c>
       <c r="B6" t="n">
         <v>43211</v>
@@ -1219,13 +1219,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>415125</v>
+        <v>414964</v>
       </c>
       <c r="R6" t="n">
-        <v>6591405</v>
+        <v>6591421</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126160263</v>
+        <v>126160239</v>
       </c>
       <c r="B7" t="n">
         <v>43211</v>
@@ -1340,13 +1340,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>414964</v>
+        <v>415125</v>
       </c>
       <c r="R7" t="n">
-        <v>6591421</v>
+        <v>6591405</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>

--- a/artfynd/A 46895-2024 artfynd.xlsx
+++ b/artfynd/A 46895-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66571393</v>
+        <v>66571350</v>
       </c>
       <c r="B2" t="n">
-        <v>42743</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -728,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>415050.8549314962</v>
+        <v>415051</v>
       </c>
       <c r="R2" t="n">
-        <v>6591470.38508611</v>
+        <v>6591470</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -758,22 +753,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-06-27</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-06-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-06-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2017-06-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,37 +785,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>66571388</v>
+        <v>126160239</v>
       </c>
       <c r="B3" t="n">
-        <v>42719</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101298</v>
+        <v>100679</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sotnätfjäril</t>
+          <t>Brun gräsfjäril</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Melitaea diamina</t>
+          <t>Coenonympha hero</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lang, 1789)</t>
+          <t>(Linnaeus, 1760)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -838,28 +818,28 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Almarskogen, Vrm</t>
+          <t>Djupdalen, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>415050.8549314962</v>
+        <v>415125</v>
       </c>
       <c r="R3" t="n">
-        <v>6591470.38508611</v>
+        <v>6591405</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -883,22 +863,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-06-27</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-06-27</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,50 +887,46 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Stig  Emilsson</t>
+          <t>Linnéa Skarped</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Stig  Emilsson</t>
+          <t>Linnéa Skarped</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>66571404</v>
+        <v>126160247</v>
       </c>
       <c r="B4" t="n">
-        <v>42543</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102923</v>
+        <v>100679</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettkantad guldvinge</t>
+          <t>Brun gräsfjäril</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycaena hippothoe</t>
+          <t>Coenonympha hero</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -963,28 +939,28 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Almarskogen, Vrm</t>
+          <t>Djupdalen, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>415050.8549314962</v>
+        <v>415118</v>
       </c>
       <c r="R4" t="n">
-        <v>6591470.38508611</v>
+        <v>6591451</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1008,22 +984,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2017-06-27</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2017-06-27</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,32 +1008,33 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Stig  Emilsson</t>
+          <t>Linnéa Skarped</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Stig  Emilsson</t>
+          <t>Linnéa Skarped</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126160247</v>
+        <v>126160258</v>
       </c>
       <c r="B5" t="n">
-        <v>43211</v>
+        <v>43450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1083,11 +1060,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
@@ -1098,10 +1071,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>415118</v>
+        <v>414944</v>
       </c>
       <c r="R5" t="n">
-        <v>6591451</v>
+        <v>6591392</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1174,11 +1147,11 @@
         <v>126160263</v>
       </c>
       <c r="B6" t="n">
-        <v>43211</v>
+        <v>43450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1292,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126160239</v>
+        <v>66571388</v>
       </c>
       <c r="B7" t="n">
-        <v>43211</v>
+        <v>43438</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1303,21 +1276,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100679</v>
+        <v>101298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Brun gräsfjäril</t>
+          <t>Sotnätfjäril</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Coenonympha hero</t>
+          <t>Melitaea diamina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1760)</t>
+          <t>(Lang, 1789)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1325,28 +1298,28 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Djupdalen, Vrm</t>
+          <t>Almarskogen, Vrm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>415125</v>
+        <v>415051</v>
       </c>
       <c r="R7" t="n">
-        <v>6591405</v>
+        <v>6591470</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1370,22 +1343,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2017-06-27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2017-06-27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1394,46 +1357,45 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linnéa Skarped</t>
+          <t>Stig  Emilsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linnéa Skarped</t>
+          <t>Stig  Emilsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126160258</v>
+        <v>66571404</v>
       </c>
       <c r="B8" t="n">
-        <v>43211</v>
+        <v>43251</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100679</v>
+        <v>102923</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brun gräsfjäril</t>
+          <t>Violettkantad guldvinge</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Coenonympha hero</t>
+          <t>Lycaena hippothoe</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1449,21 +1411,25 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Djupdalen, Vrm</t>
+          <t>Almarskogen, Vrm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>414944</v>
+        <v>415051</v>
       </c>
       <c r="R8" t="n">
-        <v>6591392</v>
+        <v>6591470</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1487,22 +1453,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2017-06-27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2017-06-27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1511,22 +1467,351 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Linnéa Skarped</t>
+          <t>Stig  Emilsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linnéa Skarped</t>
+          <t>Stig  Emilsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>66571386</v>
+      </c>
+      <c r="B9" t="n">
+        <v>43378</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>201075</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Brunfläckig pärlemorfjäril</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Boloria selene</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Almarskogen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>415051</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6591470</v>
+      </c>
+      <c r="S9" t="n">
+        <v>100</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Alster</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2017-06-27</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2017-06-27</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Stig  Emilsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Stig  Emilsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>66571400</v>
+      </c>
+      <c r="B10" t="n">
+        <v>43285</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>201143</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ängsblåvinge</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Cyaniris semiargus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Almarskogen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>415051</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6591470</v>
+      </c>
+      <c r="S10" t="n">
+        <v>100</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Alster</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2017-06-27</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2017-06-27</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Stig  Emilsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Stig  Emilsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>66571401</v>
+      </c>
+      <c r="B11" t="n">
+        <v>43309</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>201146</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Silverblåvinge</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Polyommatus amandus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Schneider, 1792)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Almarskogen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>415051</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6591470</v>
+      </c>
+      <c r="S11" t="n">
+        <v>100</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Karlstad</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Alster</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2017-06-27</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2017-06-27</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Stig  Emilsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Stig  Emilsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 46895-2024 artfynd.xlsx
+++ b/artfynd/A 46895-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66571350</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -903,6 +913,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126160239</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1024,6 +1039,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126160247</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1141,6 +1161,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126160258</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1262,6 +1287,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126160263</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1372,6 +1402,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66571388</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1482,6 +1517,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66571404</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1592,6 +1632,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66571386</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1702,6 +1747,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66571400</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1812,8 +1862,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66571401</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>